--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
